--- a/data/use_cases/uc09_120_secret_period_paid_from_non_secret_result.xlsx
+++ b/data/use_cases/uc09_120_secret_period_paid_from_non_secret_result.xlsx
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="5">
@@ -851,7 +851,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -948,7 +948,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4167,7 +4167,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Дата построения 03.07.2026</t>
+          <t>Дата построения 10.07.2026</t>
         </is>
       </c>
     </row>
